--- a/output/south_africa_generation_mix_daily.xlsx
+++ b/output/south_africa_generation_mix_daily.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -917,16 +917,16 @@
         <v>652.878875</v>
       </c>
       <c r="F9" t="n">
-        <v>599.9068333333333</v>
+        <v>599.8235000000001</v>
       </c>
       <c r="G9" t="n">
         <v>375.655375</v>
       </c>
       <c r="H9" t="n">
-        <v>1095.293291666667</v>
+        <v>1102.776291666667</v>
       </c>
       <c r="I9" t="n">
-        <v>503.50475</v>
+        <v>484.7176666666667</v>
       </c>
       <c r="J9" t="n">
         <v>47.3625</v>
@@ -955,10 +955,10 @@
         <v>447.1493333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>1135.80675</v>
+        <v>1139.28375</v>
       </c>
       <c r="I10" t="n">
-        <v>497.1769166666666</v>
+        <v>479.9018333333333</v>
       </c>
       <c r="J10" t="n">
         <v>47.39183333333333</v>
@@ -987,13 +987,109 @@
         <v>419.5679166666666</v>
       </c>
       <c r="H11" t="n">
-        <v>891.025125</v>
+        <v>890.0252083333334</v>
       </c>
       <c r="I11" t="n">
-        <v>560.3789166666667</v>
+        <v>544.627875</v>
       </c>
       <c r="J11" t="n">
         <v>47.172125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B12" t="n">
+        <v>16906.600875</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>122.7449583333333</v>
+      </c>
+      <c r="E12" t="n">
+        <v>650.5766666666667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>600.951</v>
+      </c>
+      <c r="G12" t="n">
+        <v>376.0448333333333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1137.985041666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>597.09075</v>
+      </c>
+      <c r="J12" t="n">
+        <v>47.15108333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B13" t="n">
+        <v>16634.63670833334</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>146.1078333333333</v>
+      </c>
+      <c r="E13" t="n">
+        <v>651.1357916666667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>601.398</v>
+      </c>
+      <c r="G13" t="n">
+        <v>409.3675</v>
+      </c>
+      <c r="H13" t="n">
+        <v>999.2019583333334</v>
+      </c>
+      <c r="I13" t="n">
+        <v>490.8830833333333</v>
+      </c>
+      <c r="J13" t="n">
+        <v>46.85116666666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15218.227</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>169.6042916666667</v>
+      </c>
+      <c r="E14" t="n">
+        <v>651.7128333333334</v>
+      </c>
+      <c r="F14" t="n">
+        <v>600.1207083333334</v>
+      </c>
+      <c r="G14" t="n">
+        <v>290.2275833333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1558.510583333333</v>
+      </c>
+      <c r="I14" t="n">
+        <v>624.9517916666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>47.43254166666667</v>
       </c>
     </row>
   </sheetData>
@@ -1007,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1056,7 +1152,7 @@
         <v>46280</v>
       </c>
       <c r="D4" t="n">
-        <v>7060.389333333334</v>
+        <v>7060.312958333333</v>
       </c>
     </row>
     <row r="5">
@@ -1064,7 +1160,7 @@
         <v>46281</v>
       </c>
       <c r="D5" t="n">
-        <v>7276.356541666667</v>
+        <v>7276.273208333333</v>
       </c>
     </row>
     <row r="6">
@@ -1096,7 +1192,7 @@
         <v>46285</v>
       </c>
       <c r="D9" t="n">
-        <v>7882.195666666667</v>
+        <v>7884.74775</v>
       </c>
     </row>
     <row r="10">
@@ -1110,7 +1206,7 @@
         <v>22046.701375</v>
       </c>
       <c r="D10" t="n">
-        <v>8020.176041666667</v>
+        <v>8024.222125</v>
       </c>
     </row>
     <row r="11">
@@ -1124,7 +1220,7 @@
         <v>22009.86975</v>
       </c>
       <c r="D11" t="n">
-        <v>7955.061958333333</v>
+        <v>7955.02275</v>
       </c>
     </row>
     <row r="12">
@@ -1138,7 +1234,7 @@
         <v>22016.05041666667</v>
       </c>
       <c r="D12" t="n">
-        <v>7127.279666666666</v>
+        <v>7125.68</v>
       </c>
     </row>
     <row r="13">
@@ -1152,7 +1248,7 @@
         <v>20964.82333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>6833.255583333333</v>
+        <v>6833.211708333333</v>
       </c>
     </row>
     <row r="14">
@@ -1160,13 +1256,13 @@
         <v>46290</v>
       </c>
       <c r="B14" t="n">
-        <v>19438.06275</v>
+        <v>19487.81275</v>
       </c>
       <c r="C14" t="n">
-        <v>21216.826625</v>
+        <v>21270.039625</v>
       </c>
       <c r="D14" t="n">
-        <v>7718.355083333333</v>
+        <v>7743.892708333333</v>
       </c>
     </row>
     <row r="15">
@@ -1174,13 +1270,27 @@
         <v>46291</v>
       </c>
       <c r="B15" t="n">
-        <v>19148.83733333333</v>
+        <v>19238.67066666667</v>
       </c>
       <c r="C15" t="n">
-        <v>20701.3615</v>
+        <v>20775.606875</v>
       </c>
       <c r="D15" t="n">
-        <v>8279.664375</v>
+        <v>8756.826500000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17666.642625</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19897.53754166667</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8517.416874999999</v>
       </c>
     </row>
   </sheetData>
@@ -1541,7 +1651,7 @@
         <v>71.87410320196696</v>
       </c>
       <c r="C20" t="n">
-        <v>11.86106039156081</v>
+        <v>11.8610603915608</v>
       </c>
       <c r="D20" t="n">
         <v>16.04586943088007</v>
@@ -1606,13 +1716,13 @@
         <v>46265</v>
       </c>
       <c r="B24" t="n">
-        <v>66.80931278830714</v>
+        <v>66.80349968826333</v>
       </c>
       <c r="C24" t="n">
         <v>15.16842524139862</v>
       </c>
       <c r="D24" t="n">
-        <v>17.9975852614642</v>
+        <v>18.003398361508</v>
       </c>
       <c r="E24" t="n">
         <v>0.02467670883004037</v>
@@ -1623,16 +1733,16 @@
         <v>46272</v>
       </c>
       <c r="B25" t="n">
-        <v>69.98236039997799</v>
+        <v>69.98297832387561</v>
       </c>
       <c r="C25" t="n">
         <v>13.51588603419731</v>
       </c>
       <c r="D25" t="n">
-        <v>16.41271902982432</v>
+        <v>16.41221088505596</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08903453600037754</v>
+        <v>0.08892475687111907</v>
       </c>
     </row>
     <row r="26">
@@ -1640,13 +1750,13 @@
         <v>46279</v>
       </c>
       <c r="B26" t="n">
-        <v>71.61466009147074</v>
+        <v>71.61464802350869</v>
       </c>
       <c r="C26" t="n">
-        <v>12.79325354222951</v>
+        <v>12.79330187552352</v>
       </c>
       <c r="D26" t="n">
-        <v>15.58537790663379</v>
+        <v>15.58534164130182</v>
       </c>
       <c r="E26" t="n">
         <v>0.006708459665970608</v>
@@ -1657,16 +1767,16 @@
         <v>46286</v>
       </c>
       <c r="B27" t="n">
-        <v>70.15951552048065</v>
+        <v>69.37037239125561</v>
       </c>
       <c r="C27" t="n">
-        <v>14.38928431332067</v>
+        <v>14.42082404272304</v>
       </c>
       <c r="D27" t="n">
-        <v>15.42632971859773</v>
+        <v>16.19000255368892</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02487044760095797</v>
+        <v>0.01880101233242492</v>
       </c>
     </row>
   </sheetData>
@@ -1680,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2102,70 @@
       </c>
       <c r="J9" t="n">
         <v>62.86201022146507</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>87.64705882352942</v>
+      </c>
+      <c r="D10" t="n">
+        <v>86.8627450980392</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50.17910447761194</v>
+      </c>
+      <c r="G10" t="n">
+        <v>47.95522388059702</v>
+      </c>
+      <c r="H10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>74.44633730834754</v>
+      </c>
+      <c r="J10" t="n">
+        <v>64.90630323679727</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>88.52941176470588</v>
+      </c>
+      <c r="D11" t="n">
+        <v>87.94117647058823</v>
+      </c>
+      <c r="E11" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.1044776119403</v>
+      </c>
+      <c r="G11" t="n">
+        <v>44.1044776119403</v>
+      </c>
+      <c r="H11" t="n">
+        <v>42</v>
+      </c>
+      <c r="I11" t="n">
+        <v>71.55025553662692</v>
+      </c>
+      <c r="J11" t="n">
+        <v>71.55025553662692</v>
       </c>
     </row>
   </sheetData>
@@ -2005,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2319,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
